--- a/restock_suggestions.xlsx
+++ b/restock_suggestions.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,12 +479,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -494,13 +494,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.419999999999999</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -516,28 +516,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="F3" t="n">
-        <v>557</v>
+        <v>364</v>
       </c>
       <c r="G3" t="n">
-        <v>643</v>
+        <v>494.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1122</v>
+        <v>808.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1916</v>
+        <v>1249.3</v>
       </c>
     </row>
     <row r="4">
@@ -553,12 +553,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -568,13 +568,13 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="5">
@@ -674,12 +674,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -695,7 +695,7 @@
         <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.899999999999999</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="8">
@@ -758,28 +758,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>587</v>
+        <v>335</v>
       </c>
       <c r="G9" t="n">
-        <v>632.3</v>
+        <v>379</v>
       </c>
       <c r="H9" t="n">
-        <v>1122.3</v>
+        <v>680</v>
       </c>
       <c r="I9" t="n">
-        <v>1606.3</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10">
@@ -842,28 +842,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>34.2</v>
+        <v>32.1</v>
       </c>
       <c r="H11" t="n">
-        <v>71.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>109.6</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="12">
@@ -973,28 +973,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="G14" t="n">
-        <v>474.5</v>
+        <v>329.7</v>
       </c>
       <c r="H14" t="n">
-        <v>932.1</v>
+        <v>329.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1246.7</v>
+        <v>329.7</v>
       </c>
     </row>
     <row r="15">
@@ -1010,28 +1010,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5.720000000000001</v>
+        <v>4.68</v>
       </c>
       <c r="H15" t="n">
-        <v>10.48</v>
+        <v>8.58</v>
       </c>
       <c r="I15" t="n">
-        <v>13.06</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="16">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1105,7 +1105,7 @@
         <v>20.8</v>
       </c>
       <c r="I17" t="n">
-        <v>39.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1121,28 +1121,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>W39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>24.7</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1176,10 +1186,10 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="I19" t="n">
-        <v>6.5</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="20">
@@ -1195,28 +1205,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="F20" t="n">
-        <v>500</v>
+        <v>586</v>
       </c>
       <c r="G20" t="n">
-        <v>521</v>
+        <v>590</v>
       </c>
       <c r="H20" t="n">
-        <v>1037</v>
+        <v>590</v>
       </c>
       <c r="I20" t="n">
-        <v>1037</v>
+        <v>590</v>
       </c>
     </row>
     <row r="21">
@@ -1232,12 +1242,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1247,13 +1257,13 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>7.200000000000001</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="22">
@@ -1269,28 +1279,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>46.56</v>
+        <v>32.44</v>
       </c>
       <c r="H22" t="n">
-        <v>97.88</v>
+        <v>90.22</v>
       </c>
       <c r="I22" t="n">
-        <v>159.76</v>
+        <v>179.3</v>
       </c>
     </row>
     <row r="23">
@@ -1362,19 +1372,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="F24" t="n">
-        <v>776</v>
+        <v>835</v>
       </c>
       <c r="G24" t="n">
-        <v>864.5</v>
+        <v>915.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1697.8</v>
+        <v>1896.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1895.4</v>
+        <v>2542.3</v>
       </c>
     </row>
     <row r="25">
@@ -1390,12 +1400,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1445,10 +1455,10 @@
         <v>3.52</v>
       </c>
       <c r="H26" t="n">
-        <v>8.32</v>
+        <v>7.460000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>16.34</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="27">
@@ -1464,28 +1474,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>466</v>
+        <v>397</v>
       </c>
       <c r="G27" t="n">
-        <v>499.8</v>
+        <v>486.2</v>
       </c>
       <c r="H27" t="n">
-        <v>979.5</v>
+        <v>925.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1529.4</v>
+        <v>1029.6</v>
       </c>
     </row>
     <row r="28">
@@ -1501,28 +1511,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G28" t="n">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="H28" t="n">
-        <v>493.2</v>
+        <v>363</v>
       </c>
       <c r="I28" t="n">
-        <v>550.4</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29">
@@ -1585,28 +1595,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.680000000000001</v>
+        <v>5.44</v>
       </c>
       <c r="H30" t="n">
-        <v>13.96</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>25.56</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="31">
@@ -1637,13 +1647,13 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>5.380000000000001</v>
+        <v>5.160000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>11.36</v>
+        <v>9.56</v>
       </c>
       <c r="I31" t="n">
-        <v>25.14</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="32">
@@ -1659,28 +1669,28 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="F32" t="n">
-        <v>862</v>
+        <v>689</v>
       </c>
       <c r="G32" t="n">
-        <v>925</v>
+        <v>750</v>
       </c>
       <c r="H32" t="n">
-        <v>1889.6</v>
+        <v>1518</v>
       </c>
       <c r="I32" t="n">
-        <v>2356.3</v>
+        <v>2711.9</v>
       </c>
     </row>
     <row r="33">
@@ -1696,19 +1706,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>3.5</v>
@@ -1717,7 +1727,7 @@
         <v>6.299999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>11.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="34">
@@ -1733,28 +1743,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="G34" t="n">
-        <v>135.38</v>
+        <v>123</v>
       </c>
       <c r="H34" t="n">
-        <v>194.44</v>
+        <v>247.78</v>
       </c>
       <c r="I34" t="n">
-        <v>194.44</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="35">
@@ -1770,28 +1780,28 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>6.200000000000001</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="I35" t="n">
-        <v>19.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="36">
@@ -1901,12 +1911,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1916,13 +1926,13 @@
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="H38" t="n">
-        <v>7.800000000000001</v>
+        <v>7.460000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>12.68</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="39">
@@ -2032,28 +2042,28 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.78</v>
+        <v>3.340000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>5.279999999999999</v>
+        <v>6.860000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>7.499999999999998</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="42">
@@ -2125,19 +2135,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G43" t="n">
-        <v>49.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="H43" t="n">
-        <v>96.20000000000002</v>
+        <v>120</v>
       </c>
       <c r="I43" t="n">
-        <v>119.6</v>
+        <v>179.8</v>
       </c>
     </row>
     <row r="44">
@@ -2153,28 +2163,28 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>4.68</v>
+        <v>4.04</v>
       </c>
       <c r="H44" t="n">
-        <v>10.56</v>
+        <v>7.68</v>
       </c>
       <c r="I44" t="n">
-        <v>20.92</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="45">
@@ -2190,28 +2200,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>15</v>
-      </c>
-      <c r="G45" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>36.23999999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>70.23999999999999</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2227,28 +2247,28 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F46" t="n">
-        <v>487</v>
+        <v>550</v>
       </c>
       <c r="G46" t="n">
-        <v>549</v>
+        <v>625</v>
       </c>
       <c r="H46" t="n">
-        <v>1122.7</v>
+        <v>1243.8</v>
       </c>
       <c r="I46" t="n">
-        <v>1844.2</v>
+        <v>1558.4</v>
       </c>
     </row>
     <row r="47">
@@ -2282,10 +2302,10 @@
         <v>0.3</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9000000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2310,19 +2330,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="H48" t="n">
-        <v>3.66</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>7.460000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -2338,28 +2358,28 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="G49" t="n">
-        <v>163.42</v>
+        <v>226</v>
       </c>
       <c r="H49" t="n">
-        <v>316.4</v>
+        <v>417.1</v>
       </c>
       <c r="I49" t="n">
-        <v>390.3800000000001</v>
+        <v>417.1</v>
       </c>
     </row>
     <row r="50">
@@ -2375,28 +2395,38 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>536</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1066</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1066</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1767.1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2257</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2421,19 +2451,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F51" t="n">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="G51" t="n">
-        <v>195.9</v>
+        <v>260.6</v>
       </c>
       <c r="H51" t="n">
-        <v>377.5</v>
+        <v>512.5</v>
       </c>
       <c r="I51" t="n">
-        <v>377.5</v>
+        <v>633</v>
       </c>
     </row>
     <row r="52">
@@ -2449,12 +2479,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2467,10 +2497,10 @@
         <v>1.32</v>
       </c>
       <c r="H52" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="I52" t="n">
-        <v>4.920000000000001</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="53">
@@ -2486,28 +2516,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F53" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G53" t="n">
-        <v>98.8</v>
+        <v>78.14000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>153.4</v>
+        <v>150</v>
       </c>
       <c r="I53" t="n">
-        <v>180</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="54">
@@ -2626,19 +2656,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G56" t="n">
-        <v>17.22</v>
+        <v>13</v>
       </c>
       <c r="H56" t="n">
-        <v>35.22</v>
+        <v>28.6</v>
       </c>
       <c r="I56" t="n">
-        <v>66.72</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="57">
@@ -2654,12 +2684,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2738,28 +2768,28 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G59" t="n">
-        <v>90</v>
+        <v>95.80000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>175.8</v>
+        <v>190.7</v>
       </c>
       <c r="I59" t="n">
-        <v>255.1</v>
+        <v>353.2</v>
       </c>
     </row>
     <row r="60">
@@ -2775,28 +2805,38 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" t="n">
-        <v>10</v>
-      </c>
-      <c r="G60" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="H60" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="I60" t="n">
-        <v>50.32000000000001</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -2824,16 +2864,16 @@
         <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G61" t="n">
-        <v>11.88</v>
+        <v>15.34</v>
       </c>
       <c r="H61" t="n">
-        <v>26.04</v>
+        <v>33.5</v>
       </c>
       <c r="I61" t="n">
-        <v>41.72000000000001</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2849,28 +2889,28 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W41</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F62" t="n">
-        <v>418</v>
+        <v>107</v>
       </c>
       <c r="G62" t="n">
-        <v>572</v>
+        <v>109.2</v>
       </c>
       <c r="H62" t="n">
-        <v>1008.8</v>
+        <v>109.2</v>
       </c>
       <c r="I62" t="n">
-        <v>1433.9</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="63">
@@ -2886,28 +2926,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="H63" t="n">
-        <v>16</v>
+        <v>10.4</v>
       </c>
       <c r="I63" t="n">
-        <v>32</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="64">
@@ -2923,28 +2963,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G64" t="n">
-        <v>62.9</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>128.6</v>
+        <v>123.5</v>
       </c>
       <c r="I64" t="n">
-        <v>199.6</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="65">
@@ -2960,28 +3000,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
       <c r="G65" t="n">
-        <v>3.52</v>
+        <v>1.52</v>
       </c>
       <c r="H65" t="n">
-        <v>7.040000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="I65" t="n">
-        <v>7.660000000000001</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="66">
@@ -2997,28 +3037,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G66" t="n">
-        <v>113.6</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>221.2</v>
+        <v>191.4</v>
       </c>
       <c r="I66" t="n">
-        <v>221.2</v>
+        <v>214.8</v>
       </c>
     </row>
     <row r="67">
@@ -3046,16 +3086,16 @@
         <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G67" t="n">
-        <v>19.66</v>
+        <v>17.06</v>
       </c>
       <c r="H67" t="n">
-        <v>42</v>
+        <v>35.68000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>84.22</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3071,38 +3111,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="I68" t="n">
+        <v>25.86</v>
       </c>
     </row>
     <row r="69">
@@ -3165,28 +3195,28 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="G70" t="n">
-        <v>67.2</v>
+        <v>106.9</v>
       </c>
       <c r="H70" t="n">
-        <v>100.4</v>
+        <v>215.1</v>
       </c>
       <c r="I70" t="n">
-        <v>100.4</v>
+        <v>292.1</v>
       </c>
     </row>
     <row r="71">
@@ -3211,19 +3241,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F71" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G71" t="n">
-        <v>146.5</v>
+        <v>124.5</v>
       </c>
       <c r="H71" t="n">
-        <v>292.7</v>
+        <v>259.7</v>
       </c>
       <c r="I71" t="n">
-        <v>361.6</v>
+        <v>390.2</v>
       </c>
     </row>
     <row r="72">
@@ -3239,28 +3269,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F72" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="G72" t="n">
         <v>333</v>
       </c>
       <c r="H72" t="n">
-        <v>581.6</v>
+        <v>668</v>
       </c>
       <c r="I72" t="n">
-        <v>581.6</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="73">
@@ -3276,28 +3306,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G73" t="n">
-        <v>29.5</v>
+        <v>41</v>
       </c>
       <c r="H73" t="n">
-        <v>29.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>29.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3313,28 +3343,28 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>10</v>
       </c>
       <c r="G74" t="n">
-        <v>10.76</v>
+        <v>10.32</v>
       </c>
       <c r="H74" t="n">
-        <v>28.78</v>
+        <v>21.28</v>
       </c>
       <c r="I74" t="n">
-        <v>67.78</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="75">
@@ -3350,28 +3380,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>17.28</v>
+        <v>12.04</v>
       </c>
       <c r="H75" t="n">
-        <v>35.8</v>
+        <v>25.64</v>
       </c>
       <c r="I75" t="n">
-        <v>72.7</v>
+        <v>53.62</v>
       </c>
     </row>
     <row r="76">
@@ -3387,28 +3417,38 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>14</v>
-      </c>
-      <c r="F76" t="n">
-        <v>78</v>
-      </c>
-      <c r="G76" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="H76" t="n">
-        <v>108.1</v>
-      </c>
-      <c r="I76" t="n">
-        <v>108.1</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -3424,38 +3464,28 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>34</v>
+      </c>
+      <c r="F77" t="n">
+        <v>194</v>
+      </c>
+      <c r="G77" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>212.8</v>
       </c>
     </row>
     <row r="78">
@@ -3567,16 +3597,16 @@
         <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G80" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="H80" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="I80" t="n">
-        <v>35</v>
+        <v>36.09999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3601,19 +3631,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G81" t="n">
-        <v>38.6</v>
+        <v>21.1</v>
       </c>
       <c r="H81" t="n">
-        <v>82</v>
+        <v>44.1</v>
       </c>
       <c r="I81" t="n">
-        <v>146.9</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3629,28 +3659,28 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>6.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="H82" t="n">
-        <v>18.3</v>
+        <v>14.4</v>
       </c>
       <c r="I82" t="n">
-        <v>42.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="83">
@@ -3666,38 +3696,28 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" t="n">
+        <v>46</v>
+      </c>
+      <c r="G83" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H83" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I83" t="n">
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3722,19 +3742,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="F84" t="n">
-        <v>1680</v>
+        <v>1583</v>
       </c>
       <c r="G84" t="n">
-        <v>1874.6</v>
+        <v>1957.7</v>
       </c>
       <c r="H84" t="n">
-        <v>3452.3</v>
+        <v>3775.900000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>3452.3</v>
+        <v>4639.900000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3750,28 +3770,28 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G85" t="n">
-        <v>42.56</v>
+        <v>35.2</v>
       </c>
       <c r="H85" t="n">
-        <v>73.40000000000001</v>
+        <v>69.60000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>73.40000000000001</v>
+        <v>69.60000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3881,28 +3901,38 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>15</v>
-      </c>
-      <c r="F88" t="n">
-        <v>107</v>
-      </c>
-      <c r="G88" t="n">
-        <v>121</v>
-      </c>
-      <c r="H88" t="n">
-        <v>184</v>
-      </c>
-      <c r="I88" t="n">
-        <v>184</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -4012,28 +4042,28 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="G91" t="n">
-        <v>108.6</v>
+        <v>160</v>
       </c>
       <c r="H91" t="n">
-        <v>216.2</v>
+        <v>329</v>
       </c>
       <c r="I91" t="n">
-        <v>243</v>
+        <v>656.6</v>
       </c>
     </row>
     <row r="92">
@@ -4049,28 +4079,28 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="F92" t="n">
-        <v>343</v>
+        <v>258</v>
       </c>
       <c r="G92" t="n">
-        <v>431.6</v>
+        <v>259.84</v>
       </c>
       <c r="H92" t="n">
-        <v>890.1</v>
+        <v>480.7</v>
       </c>
       <c r="I92" t="n">
-        <v>1687.3</v>
+        <v>902.8600000000001</v>
       </c>
     </row>
     <row r="93">
@@ -4086,28 +4116,28 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="H93" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -4123,28 +4153,28 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G94" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="H94" t="n">
-        <v>31.3</v>
+        <v>27.3</v>
       </c>
       <c r="I94" t="n">
-        <v>31.3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="95">
@@ -4169,19 +4199,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G95" t="n">
-        <v>27.8</v>
+        <v>20.8</v>
       </c>
       <c r="H95" t="n">
-        <v>58.2</v>
+        <v>41.6</v>
       </c>
       <c r="I95" t="n">
-        <v>64.2</v>
+        <v>58.50000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -4197,28 +4227,28 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G96" t="n">
-        <v>18.52</v>
+        <v>13.9</v>
       </c>
       <c r="H96" t="n">
-        <v>38.02</v>
+        <v>30.42</v>
       </c>
       <c r="I96" t="n">
-        <v>67.65999999999998</v>
+        <v>66.94</v>
       </c>
     </row>
     <row r="97">
@@ -4234,28 +4264,28 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F97" t="n">
-        <v>601</v>
+        <v>473</v>
       </c>
       <c r="G97" t="n">
-        <v>839</v>
+        <v>543.5000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>1532.7</v>
+        <v>954.4600000000002</v>
       </c>
       <c r="I97" t="n">
-        <v>2219.1</v>
+        <v>954.4600000000002</v>
       </c>
     </row>
     <row r="98">
@@ -4271,28 +4301,28 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G98" t="n">
-        <v>63.6</v>
+        <v>30.6</v>
       </c>
       <c r="H98" t="n">
-        <v>127.6</v>
+        <v>63.62</v>
       </c>
       <c r="I98" t="n">
-        <v>239.6</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="99">
@@ -4308,28 +4338,28 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="F99" t="n">
-        <v>314</v>
+        <v>740</v>
       </c>
       <c r="G99" t="n">
-        <v>388.8200000000001</v>
+        <v>869.7</v>
       </c>
       <c r="H99" t="n">
-        <v>388.8200000000001</v>
+        <v>1620</v>
       </c>
       <c r="I99" t="n">
-        <v>388.8200000000001</v>
+        <v>2043.8</v>
       </c>
     </row>
     <row r="100">
@@ -4345,28 +4375,28 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F100" t="n">
-        <v>446</v>
+        <v>209</v>
       </c>
       <c r="G100" t="n">
-        <v>471.2</v>
+        <v>235.2</v>
       </c>
       <c r="H100" t="n">
-        <v>832.5</v>
+        <v>303.8</v>
       </c>
       <c r="I100" t="n">
-        <v>1466.7</v>
+        <v>303.8</v>
       </c>
     </row>
     <row r="101">
@@ -4382,28 +4412,28 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F101" t="n">
-        <v>619</v>
+        <v>379</v>
       </c>
       <c r="G101" t="n">
-        <v>630.4</v>
+        <v>496.8</v>
       </c>
       <c r="H101" t="n">
-        <v>1512.2</v>
+        <v>902.0999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>2286.2</v>
+        <v>902.0999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -4419,28 +4449,28 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>556</v>
+        <v>485</v>
       </c>
       <c r="G102" t="n">
-        <v>572.8</v>
+        <v>639.1</v>
       </c>
       <c r="H102" t="n">
-        <v>1057.8</v>
+        <v>1271</v>
       </c>
       <c r="I102" t="n">
-        <v>1563.8</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="103">
@@ -4456,38 +4486,28 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>8</v>
+      </c>
+      <c r="F103" t="n">
+        <v>109</v>
+      </c>
+      <c r="G103" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="I103" t="n">
+        <v>220.6</v>
       </c>
     </row>
     <row r="104">
@@ -4503,28 +4523,28 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F104" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G104" t="n">
-        <v>721.6</v>
+        <v>690.3000000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>1463.8</v>
+        <v>1415.7</v>
       </c>
       <c r="I104" t="n">
-        <v>2308</v>
+        <v>1940.9</v>
       </c>
     </row>
     <row r="105">
@@ -4540,28 +4560,28 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F105" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G105" t="n">
-        <v>224.1</v>
+        <v>211.9</v>
       </c>
       <c r="H105" t="n">
-        <v>439.1</v>
+        <v>414.7</v>
       </c>
       <c r="I105" t="n">
-        <v>595.1</v>
+        <v>561.6000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -4577,28 +4597,28 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F106" t="n">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="G106" t="n">
-        <v>231.9</v>
+        <v>120.4</v>
       </c>
       <c r="H106" t="n">
-        <v>436.4</v>
+        <v>144.2</v>
       </c>
       <c r="I106" t="n">
-        <v>649.6999999999999</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="107">
@@ -4623,19 +4643,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F107" t="n">
-        <v>502</v>
+        <v>444</v>
       </c>
       <c r="G107" t="n">
-        <v>535.3</v>
+        <v>517.4</v>
       </c>
       <c r="H107" t="n">
-        <v>1079.6</v>
+        <v>1077.9</v>
       </c>
       <c r="I107" t="n">
-        <v>1234.3</v>
+        <v>1495.5</v>
       </c>
     </row>
     <row r="108">
@@ -4651,28 +4671,28 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F108" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G108" t="n">
-        <v>144.3</v>
+        <v>114.4</v>
       </c>
       <c r="H108" t="n">
-        <v>267.1</v>
+        <v>294.4</v>
       </c>
       <c r="I108" t="n">
-        <v>394.5</v>
+        <v>420.2</v>
       </c>
     </row>
     <row r="109">
@@ -4688,28 +4708,38 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H109" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I109" t="n">
-        <v>2.4</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -4725,28 +4755,28 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F110" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="G110" t="n">
-        <v>264.5</v>
+        <v>283.4</v>
       </c>
       <c r="H110" t="n">
-        <v>474.5</v>
+        <v>641.2</v>
       </c>
       <c r="I110" t="n">
-        <v>731.4</v>
+        <v>1039.5</v>
       </c>
     </row>
     <row r="111">
@@ -4762,28 +4792,28 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F111" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G111" t="n">
-        <v>110.6</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>223.2</v>
+        <v>105</v>
       </c>
       <c r="I111" t="n">
-        <v>306.5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112">
@@ -4799,28 +4829,28 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="G112" t="n">
-        <v>108.58</v>
+        <v>60.84</v>
       </c>
       <c r="H112" t="n">
-        <v>236.32</v>
+        <v>133.74</v>
       </c>
       <c r="I112" t="n">
-        <v>500.82</v>
+        <v>295.92</v>
       </c>
     </row>
     <row r="113">
@@ -4836,28 +4866,28 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F113" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G113" t="n">
-        <v>310.3000000000001</v>
+        <v>306</v>
       </c>
       <c r="H113" t="n">
-        <v>606.7</v>
+        <v>620.3</v>
       </c>
       <c r="I113" t="n">
-        <v>864.5</v>
+        <v>849.0999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -4873,28 +4903,28 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G114" t="n">
-        <v>11.18</v>
+        <v>18.4</v>
       </c>
       <c r="H114" t="n">
-        <v>11.18</v>
+        <v>30.4</v>
       </c>
       <c r="I114" t="n">
-        <v>11.18</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="115">
@@ -4910,28 +4940,28 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F115" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G115" t="n">
-        <v>107</v>
+        <v>83.84</v>
       </c>
       <c r="H115" t="n">
-        <v>222.4</v>
+        <v>142.5</v>
       </c>
       <c r="I115" t="n">
-        <v>344</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="116">
@@ -4947,28 +4977,28 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G116" t="n">
-        <v>31.2</v>
+        <v>27.8</v>
       </c>
       <c r="H116" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="I116" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="117">
@@ -5040,19 +5070,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G118" t="n">
-        <v>12.74</v>
+        <v>16.64</v>
       </c>
       <c r="H118" t="n">
-        <v>12.74</v>
+        <v>20.44</v>
       </c>
       <c r="I118" t="n">
-        <v>12.74</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="119">
@@ -5068,38 +5098,28 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W41</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5</v>
+      </c>
+      <c r="H119" t="n">
+        <v>5</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -5115,28 +5135,28 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F120" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G120" t="n">
-        <v>107.9</v>
+        <v>55.48</v>
       </c>
       <c r="H120" t="n">
-        <v>218.4</v>
+        <v>69.28</v>
       </c>
       <c r="I120" t="n">
-        <v>369.7</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="121">
@@ -5152,28 +5172,38 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>9</v>
-      </c>
-      <c r="G121" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="H121" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="I121" t="n">
-        <v>11.96</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -5189,28 +5219,28 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G122" t="n">
-        <v>42.06</v>
+        <v>57.2</v>
       </c>
       <c r="H122" t="n">
-        <v>63.18000000000001</v>
+        <v>114.18</v>
       </c>
       <c r="I122" t="n">
-        <v>63.18000000000001</v>
+        <v>215.7800000000001</v>
       </c>
     </row>
     <row r="123">
@@ -5226,38 +5256,28 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H123" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I123" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="124">
@@ -5273,28 +5293,28 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G124" t="n">
-        <v>60.6</v>
+        <v>40.59999999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>122.1</v>
+        <v>65.89999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>137.7</v>
+        <v>65.89999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -5310,28 +5330,28 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G125" t="n">
-        <v>25.88</v>
+        <v>24.86</v>
       </c>
       <c r="H125" t="n">
-        <v>25.88</v>
+        <v>24.86</v>
       </c>
       <c r="I125" t="n">
-        <v>25.88</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="126">
@@ -5347,28 +5367,28 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
         <v>3</v>
       </c>
       <c r="G126" t="n">
-        <v>3.62</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>7.379999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I126" t="n">
-        <v>11.28</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="127">
@@ -5403,7 +5423,7 @@
         <v>8</v>
       </c>
       <c r="I127" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128">
@@ -5419,38 +5439,28 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" t="n">
+        <v>26</v>
+      </c>
+      <c r="G128" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="H128" t="n">
+        <v>56.90000000000001</v>
+      </c>
+      <c r="I128" t="n">
+        <v>64.24000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -5475,19 +5485,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>28.1</v>
+        <v>42.76000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>41.18</v>
+        <v>87.32000000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>41.18</v>
+        <v>87.32000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -5503,28 +5513,28 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F130" t="n">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="G130" t="n">
-        <v>417.1</v>
+        <v>289.1</v>
       </c>
       <c r="H130" t="n">
-        <v>926.4000000000001</v>
+        <v>581.7</v>
       </c>
       <c r="I130" t="n">
-        <v>1850.7</v>
+        <v>581.7</v>
       </c>
     </row>
     <row r="131">
@@ -5540,28 +5550,28 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W41</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F131" t="n">
-        <v>448</v>
+        <v>30</v>
       </c>
       <c r="G131" t="n">
-        <v>468.2</v>
+        <v>73.5</v>
       </c>
       <c r="H131" t="n">
-        <v>1008.4</v>
+        <v>73.5</v>
       </c>
       <c r="I131" t="n">
-        <v>1827.4</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="132">
@@ -5577,28 +5587,28 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F132" t="n">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="G132" t="n">
-        <v>198.1</v>
+        <v>193.74</v>
       </c>
       <c r="H132" t="n">
-        <v>527.9</v>
+        <v>333.2</v>
       </c>
       <c r="I132" t="n">
-        <v>1000.9</v>
+        <v>333.2</v>
       </c>
     </row>
     <row r="133">
@@ -5614,28 +5624,28 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F133" t="n">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="G133" t="n">
-        <v>127.2</v>
+        <v>210</v>
       </c>
       <c r="H133" t="n">
-        <v>258.3</v>
+        <v>446.7</v>
       </c>
       <c r="I133" t="n">
-        <v>356.2</v>
+        <v>491.5</v>
       </c>
     </row>
     <row r="134">
@@ -5651,28 +5661,28 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F134" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G134" t="n">
-        <v>92.46000000000001</v>
+        <v>87.08</v>
       </c>
       <c r="H134" t="n">
-        <v>182.84</v>
+        <v>181.5</v>
       </c>
       <c r="I134" t="n">
-        <v>271.3000000000001</v>
+        <v>252.64</v>
       </c>
     </row>
     <row r="135">
@@ -5697,19 +5707,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F135" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="G135" t="n">
-        <v>225.6</v>
+        <v>216.44</v>
       </c>
       <c r="H135" t="n">
-        <v>479.1</v>
+        <v>431.84</v>
       </c>
       <c r="I135" t="n">
-        <v>479.1</v>
+        <v>543.9200000000001</v>
       </c>
     </row>
     <row r="136">
@@ -5725,28 +5735,28 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F136" t="n">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="G136" t="n">
-        <v>281.4</v>
+        <v>102.9</v>
       </c>
       <c r="H136" t="n">
-        <v>588.6999999999999</v>
+        <v>102.9</v>
       </c>
       <c r="I136" t="n">
-        <v>1054.2</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="137">
@@ -5762,28 +5772,28 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F137" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="G137" t="n">
-        <v>99.02</v>
+        <v>122.2</v>
       </c>
       <c r="H137" t="n">
-        <v>198.22</v>
+        <v>236.6</v>
       </c>
       <c r="I137" t="n">
-        <v>198.22</v>
+        <v>263.9</v>
       </c>
     </row>
     <row r="138">
@@ -5799,28 +5809,28 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F138" t="n">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="G138" t="n">
-        <v>163.8</v>
+        <v>203.14</v>
       </c>
       <c r="H138" t="n">
-        <v>330.9</v>
+        <v>303.8</v>
       </c>
       <c r="I138" t="n">
-        <v>330.9</v>
+        <v>303.8</v>
       </c>
     </row>
     <row r="139">
@@ -5883,28 +5893,28 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F140" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="G140" t="n">
-        <v>255.88</v>
+        <v>300.3</v>
       </c>
       <c r="H140" t="n">
-        <v>321.54</v>
+        <v>468.0000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>321.54</v>
+        <v>468.0000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -5920,28 +5930,28 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>12</v>
       </c>
       <c r="G141" t="n">
-        <v>15.6</v>
+        <v>13.8</v>
       </c>
       <c r="H141" t="n">
-        <v>27.3</v>
+        <v>21.9</v>
       </c>
       <c r="I141" t="n">
-        <v>27.3</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="142">
@@ -5957,28 +5967,28 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G142" t="n">
-        <v>30</v>
+        <v>24.2</v>
       </c>
       <c r="H142" t="n">
-        <v>36</v>
+        <v>30.90000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>36</v>
+        <v>30.90000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -5994,28 +6004,28 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G143" t="n">
-        <v>39</v>
+        <v>32.2</v>
       </c>
       <c r="H143" t="n">
-        <v>59</v>
+        <v>32.2</v>
       </c>
       <c r="I143" t="n">
-        <v>59</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="144">
@@ -6078,28 +6088,28 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F145" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G145" t="n">
-        <v>50.42</v>
+        <v>47.8</v>
       </c>
       <c r="H145" t="n">
-        <v>101.74</v>
+        <v>97.60000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>114.96</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="146">
@@ -6115,28 +6125,28 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G146" t="n">
-        <v>27</v>
+        <v>31.08</v>
       </c>
       <c r="H146" t="n">
-        <v>27</v>
+        <v>46.62</v>
       </c>
       <c r="I146" t="n">
-        <v>27</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="147">
@@ -6152,28 +6162,28 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G147" t="n">
-        <v>40</v>
+        <v>19.02</v>
       </c>
       <c r="H147" t="n">
-        <v>61</v>
+        <v>19.02</v>
       </c>
       <c r="I147" t="n">
-        <v>61</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="148">
@@ -6236,28 +6246,28 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F149" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G149" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H149" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I149" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="150">
@@ -6320,28 +6330,28 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G151" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H151" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I151" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="152">
@@ -6357,28 +6367,28 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H152" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="I152" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -6394,145 +6404,120 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>13</v>
-      </c>
-      <c r="F153" t="n">
-        <v>422</v>
-      </c>
-      <c r="G153" t="n">
-        <v>540</v>
-      </c>
-      <c r="H153" t="n">
-        <v>1063</v>
-      </c>
-      <c r="I153" t="n">
-        <v>1063</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B0F3QD6QQL</t>
+          <t>B083Y27ZG7</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>H610M S2H V2</t>
+          <t>H810M GAMING WIFI6</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="n">
-        <v>45830</v>
-      </c>
-      <c r="E154" t="n">
-        <v>15</v>
-      </c>
-      <c r="F154" t="n">
-        <v>248</v>
-      </c>
-      <c r="G154" t="n">
-        <v>299</v>
-      </c>
-      <c r="H154" t="n">
-        <v>615</v>
-      </c>
-      <c r="I154" t="n">
-        <v>1134</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>B0F3PT2QVZ</t>
+          <t>B0F3PQWDP8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>H810M S2H</t>
+          <t>W790 AI TOP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0F3PQWDP8</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>W790 AI TOP</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="D156" s="1" t="n">
-        <v>45816</v>
-      </c>
-      <c r="E156" t="n">
+          <t>W32</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>45879</v>
+      </c>
+      <c r="E155" t="n">
         <v>1</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F155" t="n">
         <v>4</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G155" t="n">
         <v>4</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H155" t="n">
         <v>8</v>
       </c>
-      <c r="I156" t="n">
-        <v>16</v>
+      <c r="I155" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
